--- a/manual/jfk_files_index_manual.xlsx
+++ b/manual/jfk_files_index_manual.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29704"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/denizguvenol/Desktop/thesis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/zeynepdeniz_guvenol_student_kuleuven_be/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73CA273C-30DC-504D-9AC3-18CB8100CC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CE41F9A-C70E-5248-B8BE-45AB9D7D3DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{A4B08258-905E-0441-97CD-A4DE3F88DBFA}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{A4B08258-905E-0441-97CD-A4DE3F88DBFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="114">
   <si>
     <t>filename</t>
   </si>
@@ -234,13 +234,157 @@
   </si>
   <si>
     <t>104-10326-10080.pdf</t>
+  </si>
+  <si>
+    <t>104-10326-10082.pdf</t>
+  </si>
+  <si>
+    <t>two-page classified cable, uniform layout, heavy scan noise, dense operational text</t>
+  </si>
+  <si>
+    <t>104-10326-10092.pdf</t>
+  </si>
+  <si>
+    <t>104-10335-10001.pdf</t>
+  </si>
+  <si>
+    <t>arrb_request_packet</t>
+  </si>
+  <si>
+    <t>facsimile transmittal and ARRB request packet, mixed letter and list formats, handwritten signatures, heavy scan noise, extremely dense enumerations</t>
+  </si>
+  <si>
+    <t>104-10423-10337.pdf</t>
+  </si>
+  <si>
+    <t>book_dispatch_with_testimony</t>
+  </si>
+  <si>
+    <t>long CIA book dispatch with attached Warren Commission testimony excerpts, dense verbatim dialogue, repetitive formatting, heavy scan noise</t>
+  </si>
+  <si>
+    <t>124-10062-10456.pdf</t>
+  </si>
+  <si>
+    <t>identification_form_with_memo</t>
+  </si>
+  <si>
+    <t>identification form with attached FBI memorandum, heavy handwritten annotations, classification stamps, mixed layout, degraded scan</t>
+  </si>
+  <si>
+    <t>124-10163-10134.pdf</t>
+  </si>
+  <si>
+    <t>identification form with attached CIA memorandum, heavy handwritten annotations, redactions, classification stamps, degraded scan</t>
+  </si>
+  <si>
+    <t>124-10185-10214.pdf</t>
+  </si>
+  <si>
+    <t>oversight_correspondence_packet</t>
+  </si>
+  <si>
+    <t>senate intelligence committee correspondence and memoranda, mixed letter and memo layouts, handwritten annotations and signatures, classification stamps, heavy scan noise</t>
+  </si>
+  <si>
+    <t>124-10274-10014_multirif_redacted.pdf</t>
+  </si>
+  <si>
+    <t>multirif_redacted_dossier</t>
+  </si>
+  <si>
+    <t>large multirif intelligence dossier with mixed document types, extensive redactions, tables, handwriting, stamps, and severe scan degradation</t>
+  </si>
+  <si>
+    <t>124-90140-10071.pdf</t>
+  </si>
+  <si>
+    <t>identification form with attached FBI memorandum, extensive handwritten annotations, classification stamps, mixed layout, degraded scan</t>
+  </si>
+  <si>
+    <t>157-10011-10066.pdf</t>
+  </si>
+  <si>
+    <t>intelligence_report</t>
+  </si>
+  <si>
+    <t>long intelligence report with dense narrative text, handwritten annotations, redactions, classification stamps, and heavy scan degradation</t>
+  </si>
+  <si>
+    <t>176-10036-10078.pdf</t>
+  </si>
+  <si>
+    <t>identification_form_with_telegram</t>
+  </si>
+  <si>
+    <t>identification form with attached CIA telegram information report, dense narrative text, classification stamps, heavy scan degradation</t>
+  </si>
+  <si>
+    <t>180-10068-10317.pdf</t>
+  </si>
+  <si>
+    <t>personnel_records_packet</t>
+  </si>
+  <si>
+    <t>personnel and payroll records packet with multiple form layouts, handwritten entries, tables, stamps, and scan degradation</t>
+  </si>
+  <si>
+    <t>180-10070-10148.pdf</t>
+  </si>
+  <si>
+    <t>personnel_records_dossier</t>
+  </si>
+  <si>
+    <t>personnel and payroll records dossier with multiple form layouts, tables, handwritten notes, signatures, stamps, and scan degradation</t>
+  </si>
+  <si>
+    <t>180-10147-10264.pdf</t>
+  </si>
+  <si>
+    <t>personnel and payroll records packet with identification form, multiple payroll authorization forms, tables, handwritten signatures, stamps, and scan degradation</t>
+  </si>
+  <si>
+    <t>194-10002-10203_redacted.pdf</t>
+  </si>
+  <si>
+    <t>fbi_investigative_file</t>
+  </si>
+  <si>
+    <t>fbi investigative file with dense narrative reports, financial tables, heavy redactions, classification stamps, and severe scan degradation</t>
+  </si>
+  <si>
+    <t>194-10004-10397.pdf</t>
+  </si>
+  <si>
+    <t>identification_form_with_agent_report</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>identification form with attached FBI agent report, clean typewritten text, minimal handwriting, good scan quality</t>
+  </si>
+  <si>
+    <t>194-10006-10195.pdf</t>
+  </si>
+  <si>
+    <t>identification_form_with_memorandum</t>
+  </si>
+  <si>
+    <t>identification form with attached memorandum, clean typewritten text, uniform layout, good scan quality</t>
+  </si>
+  <si>
+    <t>194-10007-10424.pdf</t>
+  </si>
+  <si>
+    <t>identification form with attached agent report and sworn statement, clean typewritten text, minimal handwriting, fair scan quality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -613,14 +757,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9DBE3E-ED76-7B4C-BA54-E2D0ADBBC451}">
-  <dimension ref="A1:P21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P39"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,7 +812,7 @@
       </c>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -715,7 +859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -762,7 +906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -809,7 +953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -856,7 +1000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -903,7 +1047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -950,7 +1094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -997,7 +1141,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1044,7 +1188,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1091,7 +1235,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1138,7 +1282,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1185,7 +1329,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -1232,7 +1376,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -1279,7 +1423,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1326,7 +1470,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -1373,7 +1517,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1420,7 +1564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -1467,7 +1611,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1514,7 +1658,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -1561,7 +1705,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -1606,6 +1750,852 @@
       </c>
       <c r="O21" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25">
+        <v>52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29">
+        <v>397</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="s">
+        <v>27</v>
+      </c>
+      <c r="O32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36">
+        <v>136</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
